--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="559">
   <si>
     <t xml:space="preserve">ΚΥΑ 1689/2025 και Microsoft 365: checklist συμμόρφωσης</t>
   </si>
@@ -728,9 +728,6 @@
   </si>
   <si>
     <t xml:space="preserve">Microsoft Entra ID Governance (lifecycle workflows)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/</t>
   </si>
   <si>
     <t xml:space="preserve">13.στ</t>
@@ -3892,9 +3889,7 @@
         <v>228</v>
       </c>
       <c r="J41" s="8"/>
-      <c r="K41" s="8" t="s">
-        <v>229</v>
-      </c>
+      <c r="K41" s="8"/>
       <c r="L41" s="9"/>
       <c r="M41" s="10"/>
       <c r="N41" s="10"/>
@@ -3903,7 +3898,7 @@
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>13</v>
@@ -3915,21 +3910,21 @@
         <v>45</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G42" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>233</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L42" s="9"/>
       <c r="M42" s="10"/>
@@ -3939,7 +3934,7 @@
     </row>
     <row r="43" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>13</v>
@@ -3951,21 +3946,21 @@
         <v>45</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G43" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="H43" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>238</v>
       </c>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L43" s="9"/>
       <c r="M43" s="10"/>
@@ -3975,7 +3970,7 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>13</v>
@@ -3987,19 +3982,19 @@
         <v>45</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G44" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="H44" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="H44" s="8" t="s">
+      <c r="I44" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>244</v>
       </c>
       <c r="J44" s="8"/>
       <c r="K44" s="8" t="s">
@@ -4013,33 +4008,33 @@
     </row>
     <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B45" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C45" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>247</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G45" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="H45" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>249</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L45" s="9"/>
       <c r="M45" s="10"/>
@@ -4049,35 +4044,35 @@
     </row>
     <row r="46" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B46" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G46" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H46" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="H46" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>254</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>255</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="10"/>
@@ -4087,35 +4082,35 @@
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B47" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G47" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="H47" s="8" t="s">
         <v>259</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>260</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="K47" s="8" t="s">
         <v>261</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>262</v>
       </c>
       <c r="L47" s="9"/>
       <c r="M47" s="10"/>
@@ -4125,28 +4120,28 @@
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B48" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G48" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="H48" s="8" t="s">
         <v>265</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>266</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
@@ -4161,28 +4156,28 @@
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B49" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>269</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G49" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="H49" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>271</v>
       </c>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -4195,35 +4190,35 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B50" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G50" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="H50" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="H50" s="8" t="s">
+      <c r="I50" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>276</v>
       </c>
       <c r="J50" s="8"/>
       <c r="K50" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L50" s="9"/>
       <c r="M50" s="10"/>
@@ -4233,31 +4228,31 @@
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B51" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G51" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="H51" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="H51" s="8" t="s">
+      <c r="I51" s="8" t="s">
         <v>281</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>282</v>
       </c>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
@@ -4269,31 +4264,31 @@
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B52" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G52" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="H52" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="I52" s="8" t="s">
         <v>286</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>287</v>
       </c>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
@@ -4305,33 +4300,33 @@
     </row>
     <row r="53" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B53" s="7" t="n">
         <v>16</v>
       </c>
       <c r="C53" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" s="8" t="s">
         <v>289</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G53" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H53" s="8" t="s">
         <v>291</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>292</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L53" s="9"/>
       <c r="M53" s="10"/>
@@ -4341,19 +4336,19 @@
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B54" s="7" t="n">
         <v>16</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>25</v>
@@ -4375,33 +4370,33 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B55" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>297</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>298</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G55" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="H55" s="8" t="s">
         <v>299</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>300</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L55" s="9"/>
       <c r="M55" s="10"/>
@@ -4411,33 +4406,33 @@
     </row>
     <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B56" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G56" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H56" s="8" t="s">
         <v>304</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>305</v>
       </c>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
       <c r="K56" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L56" s="9"/>
       <c r="M56" s="10"/>
@@ -4447,33 +4442,33 @@
     </row>
     <row r="57" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B57" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G57" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="H57" s="8" t="s">
         <v>309</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>310</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
       <c r="K57" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L57" s="9"/>
       <c r="M57" s="10"/>
@@ -4483,33 +4478,33 @@
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B58" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G58" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="H58" s="8" t="s">
         <v>314</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>315</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L58" s="9"/>
       <c r="M58" s="10"/>
@@ -4519,37 +4514,37 @@
     </row>
     <row r="59" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B59" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G59" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H59" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="H59" s="8" t="s">
+      <c r="I59" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="J59" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="J59" s="8" t="s">
-        <v>322</v>
-      </c>
       <c r="K59" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L59" s="9"/>
       <c r="M59" s="10"/>
@@ -4559,33 +4554,33 @@
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B60" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G60" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="H60" s="8" t="s">
         <v>325</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>326</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L60" s="9"/>
       <c r="M60" s="10"/>
@@ -4595,19 +4590,19 @@
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B61" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>25</v>
@@ -4616,7 +4611,7 @@
         <v>92</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
@@ -4629,19 +4624,19 @@
     </row>
     <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B62" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C62" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>332</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>333</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>25</v>
@@ -4650,7 +4645,7 @@
         <v>92</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
@@ -4663,28 +4658,28 @@
     </row>
     <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B63" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G63" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="H63" s="8" t="s">
         <v>337</v>
-      </c>
-      <c r="H63" s="8" t="s">
-        <v>338</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
@@ -4697,28 +4692,28 @@
     </row>
     <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B64" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G64" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H64" s="8" t="s">
         <v>341</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>342</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
@@ -4733,28 +4728,28 @@
     </row>
     <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G65" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="H65" s="8" t="s">
         <v>345</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>346</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
@@ -4769,28 +4764,28 @@
     </row>
     <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
@@ -4803,33 +4798,33 @@
     </row>
     <row r="67" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B67" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L67" s="9"/>
       <c r="M67" s="10"/>
@@ -4839,19 +4834,19 @@
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B68" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C68" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="8" t="s">
         <v>355</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>356</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>25</v>
@@ -4860,7 +4855,7 @@
         <v>92</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
@@ -4873,35 +4868,35 @@
     </row>
     <row r="69" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B69" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G69" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="H69" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="I69" s="8" t="s">
         <v>361</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>362</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L69" s="9"/>
       <c r="M69" s="10"/>
@@ -4911,33 +4906,33 @@
     </row>
     <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B70" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G70" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="H70" s="8" t="s">
         <v>366</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>367</v>
       </c>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="L70" s="9"/>
       <c r="M70" s="10"/>
@@ -4947,28 +4942,28 @@
     </row>
     <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B71" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G71" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="H71" s="8" t="s">
         <v>371</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>372</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
@@ -4983,33 +4978,33 @@
     </row>
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B72" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G72" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="H72" s="8" t="s">
         <v>375</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>376</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L72" s="9"/>
       <c r="M72" s="10"/>
@@ -5019,28 +5014,28 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B73" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G73" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="H73" s="8" t="s">
         <v>380</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>381</v>
       </c>
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
@@ -5053,33 +5048,33 @@
     </row>
     <row r="74" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B74" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G74" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="H74" s="8" t="s">
         <v>384</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>385</v>
       </c>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
       <c r="K74" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L74" s="9"/>
       <c r="M74" s="10"/>
@@ -5089,35 +5084,35 @@
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B75" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G75" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="H75" s="8" t="s">
         <v>389</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>390</v>
       </c>
       <c r="I75" s="8"/>
       <c r="J75" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="K75" s="8" t="s">
         <v>391</v>
-      </c>
-      <c r="K75" s="8" t="s">
-        <v>392</v>
       </c>
       <c r="L75" s="9"/>
       <c r="M75" s="10"/>
@@ -5127,33 +5122,33 @@
     </row>
     <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B76" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G76" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="H76" s="8" t="s">
         <v>395</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>396</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
       <c r="K76" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="L76" s="9"/>
       <c r="M76" s="10"/>
@@ -5163,31 +5158,31 @@
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B77" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G77" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="H77" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="H77" s="8" t="s">
+      <c r="I77" s="8" t="s">
         <v>401</v>
-      </c>
-      <c r="I77" s="8" t="s">
-        <v>402</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
@@ -5199,19 +5194,19 @@
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B78" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>25</v>
@@ -5233,35 +5228,35 @@
     </row>
     <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B79" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C79" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="8" t="s">
         <v>406</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>407</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G79" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="H79" s="8" t="s">
         <v>408</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>409</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="K79" s="8" t="s">
         <v>410</v>
-      </c>
-      <c r="K79" s="8" t="s">
-        <v>411</v>
       </c>
       <c r="L79" s="9"/>
       <c r="M79" s="10"/>
@@ -5271,31 +5266,31 @@
     </row>
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B80" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G80" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="H80" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="I80" s="8" t="s">
         <v>415</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>416</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
@@ -5307,33 +5302,33 @@
     </row>
     <row r="81" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B81" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G81" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="H81" s="8" t="s">
         <v>419</v>
-      </c>
-      <c r="H81" s="8" t="s">
-        <v>420</v>
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="8"/>
       <c r="K81" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L81" s="9"/>
       <c r="M81" s="10"/>
@@ -5343,31 +5338,31 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B82" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G82" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="H82" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="H82" s="8" t="s">
+      <c r="I82" s="8" t="s">
         <v>425</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>426</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
@@ -5379,33 +5374,33 @@
     </row>
     <row r="83" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B83" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G83" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="H83" s="8" t="s">
         <v>429</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>430</v>
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="8"/>
       <c r="K83" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L83" s="9"/>
       <c r="M83" s="10"/>
@@ -5415,37 +5410,37 @@
     </row>
     <row r="84" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B84" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C84" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E84" s="8" t="s">
         <v>433</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>434</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G84" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="H84" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="H84" s="8" t="s">
+      <c r="I84" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="I84" s="8" t="s">
+      <c r="J84" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="J84" s="8" t="s">
+      <c r="K84" s="8" t="s">
         <v>438</v>
-      </c>
-      <c r="K84" s="8" t="s">
-        <v>439</v>
       </c>
       <c r="L84" s="9"/>
       <c r="M84" s="10"/>
@@ -5455,28 +5450,28 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G85" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="H85" s="8" t="s">
         <v>442</v>
-      </c>
-      <c r="H85" s="8" t="s">
-        <v>443</v>
       </c>
       <c r="I85" s="8"/>
       <c r="J85" s="8"/>
@@ -5489,31 +5484,31 @@
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B86" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G86" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="H86" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="H86" s="8" t="s">
-        <v>447</v>
-      </c>
       <c r="I86" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
@@ -5525,19 +5520,19 @@
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B87" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C87" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E87" s="8" t="s">
         <v>449</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>450</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>25</v>
@@ -5546,7 +5541,7 @@
         <v>92</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
@@ -5559,35 +5554,35 @@
     </row>
     <row r="88" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B88" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G88" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="H88" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>455</v>
       </c>
       <c r="I88" s="8"/>
       <c r="J88" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="K88" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="K88" s="8" t="s">
-        <v>457</v>
       </c>
       <c r="L88" s="9"/>
       <c r="M88" s="10"/>
@@ -5597,33 +5592,33 @@
     </row>
     <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B89" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G89" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="H89" s="8" t="s">
         <v>460</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>461</v>
       </c>
       <c r="I89" s="8"/>
       <c r="J89" s="8"/>
       <c r="K89" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="L89" s="9"/>
       <c r="M89" s="10"/>
@@ -5633,31 +5628,31 @@
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B90" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G90" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="H90" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="H90" s="8" t="s">
+      <c r="I90" s="8" t="s">
         <v>466</v>
-      </c>
-      <c r="I90" s="8" t="s">
-        <v>467</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
@@ -5669,19 +5664,19 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B91" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>25</v>
@@ -5703,28 +5698,28 @@
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B92" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C92" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E92" s="8" t="s">
         <v>471</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>472</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G92" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="H92" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>474</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
@@ -5737,28 +5732,28 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B93" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G93" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="H93" s="8" t="s">
         <v>477</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>478</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
@@ -5771,28 +5766,28 @@
     </row>
     <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B94" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
@@ -5805,28 +5800,28 @@
     </row>
     <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B95" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="8"/>
@@ -5839,28 +5834,28 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B96" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
@@ -5873,19 +5868,19 @@
     </row>
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B97" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>25</v>
@@ -5907,33 +5902,33 @@
     </row>
     <row r="98" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B98" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C98" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E98" s="8" t="s">
         <v>491</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>492</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G98" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H98" s="8" t="s">
         <v>493</v>
-      </c>
-      <c r="H98" s="8" t="s">
-        <v>494</v>
       </c>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
       <c r="K98" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L98" s="9"/>
       <c r="M98" s="10"/>
@@ -5943,28 +5938,28 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B99" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G99" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="H99" s="8" t="s">
         <v>498</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>499</v>
       </c>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
@@ -5979,37 +5974,37 @@
     </row>
     <row r="100" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B100" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G100" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="H100" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="H100" s="8" t="s">
+      <c r="I100" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="I100" s="8" t="s">
+      <c r="J100" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="J100" s="8" t="s">
+      <c r="K100" s="8" t="s">
         <v>505</v>
-      </c>
-      <c r="K100" s="8" t="s">
-        <v>506</v>
       </c>
       <c r="L100" s="9"/>
       <c r="M100" s="10"/>
@@ -6019,34 +6014,34 @@
     </row>
     <row r="101" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B101" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G101" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="H101" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="H101" s="8" t="s">
+      <c r="I101" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="I101" s="8" t="s">
+      <c r="J101" s="8" t="s">
         <v>511</v>
-      </c>
-      <c r="J101" s="8" t="s">
-        <v>512</v>
       </c>
       <c r="K101" s="8" t="s">
         <v>73</v>
@@ -6059,33 +6054,33 @@
     </row>
     <row r="102" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B102" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>21</v>
       </c>
       <c r="G102" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="H102" s="8" t="s">
         <v>515</v>
-      </c>
-      <c r="H102" s="8" t="s">
-        <v>516</v>
       </c>
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
       <c r="K102" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L102" s="9"/>
       <c r="M102" s="10"/>
@@ -6095,19 +6090,19 @@
     </row>
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B103" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>25</v>
@@ -6116,7 +6111,7 @@
         <v>92</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
@@ -6129,19 +6124,19 @@
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B104" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C104" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E104" s="8" t="s">
         <v>522</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>523</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>25</v>
@@ -6150,7 +6145,7 @@
         <v>92</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
@@ -6163,19 +6158,19 @@
     </row>
     <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B105" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>25</v>
@@ -6184,7 +6179,7 @@
         <v>92</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
@@ -6197,19 +6192,19 @@
     </row>
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B106" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>25</v>
@@ -6218,7 +6213,7 @@
         <v>92</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
@@ -6231,19 +6226,19 @@
     </row>
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B107" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>25</v>
@@ -6252,7 +6247,7 @@
         <v>92</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
@@ -6265,31 +6260,31 @@
     </row>
     <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B108" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G108" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="H108" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="H108" s="8" t="s">
+      <c r="I108" s="8" t="s">
         <v>537</v>
-      </c>
-      <c r="I108" s="8" t="s">
-        <v>538</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
@@ -6301,34 +6296,34 @@
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B109" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G109" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="H109" s="8" t="s">
         <v>541</v>
-      </c>
-      <c r="H109" s="8" t="s">
-        <v>542</v>
       </c>
       <c r="I109" s="8" t="s">
         <v>222</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K109" s="8"/>
       <c r="L109" s="9"/>
@@ -6339,28 +6334,28 @@
     </row>
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B110" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>45</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>25</v>
       </c>
       <c r="G110" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="H110" s="8" t="s">
         <v>546</v>
-      </c>
-      <c r="H110" s="8" t="s">
-        <v>547</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
@@ -6373,19 +6368,19 @@
     </row>
     <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B111" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>25</v>
@@ -6394,7 +6389,7 @@
         <v>92</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
@@ -6407,19 +6402,19 @@
     </row>
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B112" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>75</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>25</v>
@@ -6484,22 +6479,22 @@
         <v>31</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>556</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>557</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>558</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>18</v>
@@ -6870,7 +6865,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C12" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A12)</f>
@@ -6906,7 +6901,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A13)</f>
@@ -6942,7 +6937,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C14" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A14)</f>
@@ -6978,7 +6973,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A15)</f>
@@ -7014,7 +7009,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A16)</f>
@@ -7050,7 +7045,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C17" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A17)</f>
@@ -7086,7 +7081,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A18)</f>
@@ -7122,7 +7117,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C19" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A19)</f>
@@ -7158,7 +7153,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C20" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A20)</f>
@@ -7194,7 +7189,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A21)</f>
@@ -7230,7 +7225,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A22)</f>
@@ -7266,7 +7261,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A23)</f>
@@ -7300,7 +7295,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13"/>
       <c r="B24" s="14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">SUM(C2:C23)</f>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -39,7 +39,7 @@
     <t xml:space="preserve">Συντάκτης</t>
   </si>
   <si>
-    <t xml:space="preserve">Δημοσθένης Αττέια, Microsoft 365 Security Insights. Η πλήρης σελίδα με φίλτρα και links: https://thecybersec.gr/nis2/</t>
+    <t xml:space="preserve">Δημοσθένης Αττέια, Microsoft 365 Security Insights. Η πλήρης σελίδα με φίλτρα και links: https://thecybersec.gr/kya-1689-2025/</t>
   </si>
   <si>
     <t xml:space="preserve">Έκδοση</t>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="572">
   <si>
     <t xml:space="preserve">ΚΥΑ 1689/2025 και Microsoft 365: checklist συμμόρφωσης</t>
   </si>
@@ -52,6 +52,45 @@
   </si>
   <si>
     <t xml:space="preserve">Η αντιστοίχιση είναι επαγγελματική ερμηνεία και όχι νομική συμβουλή. Μια ρύθμιση υποστηρίζει μια απαίτηση, δεν αποδεικνύει από μόνη της συμμόρφωση. Οι περιγραφές είναι σύντομες παραφράσεις. Για το ακριβές κείμενο ισχύει το ΦΕΚ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πνευματικά δικαιώματα και όροι χρήσης</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δικαιούχος</t>
+  </si>
+  <si>
+    <t xml:space="preserve">© 2026 Δημοσθένης Αττέια, thecybersec.gr. Με επιφύλαξη παντός δικαιώματος.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τι προστατεύεται</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η αντιστοίχιση των απαιτήσεων με ρυθμίσεις και εργαλεία της Microsoft, οι περιγραφές, τα τεκμήρια, τα σχόλια και η δομή του αρχείου είναι πρωτότυπο έργο του συντάκτη και προστατεύονται από τον ν. 2121/1993. Το κείμενο της ΚΥΑ 1689/2025 είναι δημόσιο έγγραφο και δεν αποτελεί αντικείμενο αυτής της προστασίας.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τι επιτρέπεται</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η χρήση και η συμπλήρωση του αρχείου για τις εσωτερικές ανάγκες του οργανισμού σας, καθώς και η επίδειξή του σε ελεγκτές και αρμόδιες αρχές στο πλαίσιο ελέγχου.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Τι απαγορεύεται χωρίς γραπτή άδεια του συντάκτη</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Η αναδημοσίευση, η αναδιανομή και η ανάρτηση του αρχείου ή τμήματός του σε ιστότοπους, πλατφόρμες ή μέσα κοινωνικής δικτύωσης. Η εμπορική εκμετάλλευση, μαζί με την ενσωμάτωσή του σε προϊόντα, υπηρεσίες, εκπαιδευτικό υλικό ή παραδοτέα προς τρίτους. Η αφαίρεση ή η αλλοίωση της αναφοράς στον συντάκτη και στην πηγή.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Πώς το μοιράζεστε</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Με παραπομπή στη σελίδα https://thecybersec.gr/kya-1689-2025/, από όπου ο καθένας κατεβάζει την τρέχουσα έκδοση.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Επικοινωνία για άδεια χρήσης</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Μέσω LinkedIn: https://www.linkedin.com/in/dimosthenisatteia/</t>
   </si>
   <si>
     <t xml:space="preserve">Πώς συμπληρώνεται</t>
@@ -2249,7 +2288,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -2298,13 +2337,13 @@
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2312,7 +2351,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -2328,7 +2367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -2345,24 +2384,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="5"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -2378,12 +2417,70 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2428,83 +2525,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B2" s="7" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="10"/>
@@ -2514,33 +2611,33 @@
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="10"/>
@@ -2550,28 +2647,28 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -2584,33 +2681,33 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
@@ -2620,33 +2717,33 @@
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="10"/>
@@ -2656,33 +2753,33 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L7" s="9"/>
       <c r="M7" s="10"/>
@@ -2692,35 +2789,35 @@
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="L8" s="9"/>
       <c r="M8" s="10"/>
@@ -2730,28 +2827,28 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -2764,28 +2861,28 @@
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -2798,28 +2895,28 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -2832,33 +2929,33 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="10"/>
@@ -2868,28 +2965,28 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
@@ -2902,31 +2999,31 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -2938,33 +3035,33 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L15" s="9"/>
       <c r="M15" s="10"/>
@@ -2974,28 +3071,28 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
@@ -3008,33 +3105,33 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B17" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L17" s="9"/>
       <c r="M17" s="10"/>
@@ -3044,28 +3141,28 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
@@ -3078,33 +3175,33 @@
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L19" s="9"/>
       <c r="M19" s="10"/>
@@ -3114,33 +3211,33 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L20" s="9"/>
       <c r="M20" s="10"/>
@@ -3150,33 +3247,33 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="10"/>
@@ -3186,28 +3283,28 @@
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
@@ -3220,28 +3317,28 @@
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
@@ -3254,28 +3351,28 @@
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
@@ -3288,28 +3385,28 @@
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
@@ -3322,37 +3419,37 @@
     </row>
     <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="L26" s="9"/>
       <c r="M26" s="10"/>
@@ -3362,33 +3459,33 @@
     </row>
     <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="8"/>
       <c r="K27" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="L27" s="9"/>
       <c r="M27" s="10"/>
@@ -3398,33 +3495,33 @@
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="L28" s="9"/>
       <c r="M28" s="10"/>
@@ -3434,28 +3531,28 @@
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -3468,28 +3565,28 @@
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
@@ -3502,33 +3599,33 @@
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
       <c r="K31" s="8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="L31" s="9"/>
       <c r="M31" s="10"/>
@@ -3538,33 +3635,33 @@
     </row>
     <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="L32" s="9"/>
       <c r="M32" s="10"/>
@@ -3574,33 +3671,33 @@
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="8" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="10"/>
@@ -3610,28 +3707,28 @@
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B34" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
@@ -3644,33 +3741,33 @@
     </row>
     <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="10"/>
@@ -3680,28 +3777,28 @@
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -3714,33 +3811,33 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B37" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="L37" s="9"/>
       <c r="M37" s="10"/>
@@ -3750,33 +3847,33 @@
     </row>
     <row r="38" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B38" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="L38" s="9"/>
       <c r="M38" s="10"/>
@@ -3786,35 +3883,35 @@
     </row>
     <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B39" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="L39" s="9"/>
       <c r="M39" s="10"/>
@@ -3824,35 +3921,35 @@
     </row>
     <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="J40" s="8"/>
       <c r="K40" s="8" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="L40" s="9"/>
       <c r="M40" s="10"/>
@@ -3862,31 +3959,31 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
@@ -3898,33 +3995,33 @@
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="L42" s="9"/>
       <c r="M42" s="10"/>
@@ -3934,33 +4031,33 @@
     </row>
     <row r="43" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="L43" s="9"/>
       <c r="M43" s="10"/>
@@ -3970,35 +4067,35 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="J44" s="8"/>
       <c r="K44" s="8" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="L44" s="9"/>
       <c r="M44" s="10"/>
@@ -4008,33 +4105,33 @@
     </row>
     <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B45" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="L45" s="9"/>
       <c r="M45" s="10"/>
@@ -4044,35 +4141,35 @@
     </row>
     <row r="46" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B46" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="10"/>
@@ -4082,35 +4179,35 @@
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B47" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="L47" s="9"/>
       <c r="M47" s="10"/>
@@ -4120,33 +4217,33 @@
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B48" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L48" s="9"/>
       <c r="M48" s="10"/>
@@ -4156,28 +4253,28 @@
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B49" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -4190,35 +4287,35 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="B50" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="J50" s="8"/>
       <c r="K50" s="8" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="L50" s="9"/>
       <c r="M50" s="10"/>
@@ -4228,31 +4325,31 @@
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B51" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
@@ -4264,31 +4361,31 @@
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="B52" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
@@ -4300,33 +4397,33 @@
     </row>
     <row r="53" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B53" s="7" t="n">
         <v>16</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="L53" s="9"/>
       <c r="M53" s="10"/>
@@ -4336,28 +4433,28 @@
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B54" s="7" t="n">
         <v>16</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
@@ -4370,33 +4467,33 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B55" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
       <c r="K55" s="8" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="L55" s="9"/>
       <c r="M55" s="10"/>
@@ -4406,33 +4503,33 @@
     </row>
     <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B56" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
       <c r="K56" s="8" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="L56" s="9"/>
       <c r="M56" s="10"/>
@@ -4442,33 +4539,33 @@
     </row>
     <row r="57" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B57" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
       <c r="K57" s="8" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="L57" s="9"/>
       <c r="M57" s="10"/>
@@ -4478,33 +4575,33 @@
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B58" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="L58" s="9"/>
       <c r="M58" s="10"/>
@@ -4514,37 +4611,37 @@
     </row>
     <row r="59" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B59" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="L59" s="9"/>
       <c r="M59" s="10"/>
@@ -4554,33 +4651,33 @@
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B60" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
       <c r="K60" s="8" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="L60" s="9"/>
       <c r="M60" s="10"/>
@@ -4590,28 +4687,28 @@
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B61" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
@@ -4624,28 +4721,28 @@
     </row>
     <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B62" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
@@ -4658,28 +4755,28 @@
     </row>
     <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B63" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
@@ -4692,33 +4789,33 @@
     </row>
     <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B64" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L64" s="9"/>
       <c r="M64" s="10"/>
@@ -4728,33 +4825,33 @@
     </row>
     <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="8" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="L65" s="9"/>
       <c r="M65" s="10"/>
@@ -4764,28 +4861,28 @@
     </row>
     <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
@@ -4798,33 +4895,33 @@
     </row>
     <row r="67" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="B67" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
       <c r="K67" s="8" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="L67" s="9"/>
       <c r="M67" s="10"/>
@@ -4834,28 +4931,28 @@
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B68" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
@@ -4868,35 +4965,35 @@
     </row>
     <row r="69" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="B69" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="8" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="L69" s="9"/>
       <c r="M69" s="10"/>
@@ -4906,33 +5003,33 @@
     </row>
     <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="B70" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="L70" s="9"/>
       <c r="M70" s="10"/>
@@ -4942,33 +5039,33 @@
     </row>
     <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="B71" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="L71" s="9"/>
       <c r="M71" s="10"/>
@@ -4978,33 +5075,33 @@
     </row>
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B72" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
       <c r="K72" s="8" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="L72" s="9"/>
       <c r="M72" s="10"/>
@@ -5014,28 +5111,28 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="B73" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
@@ -5048,33 +5145,33 @@
     </row>
     <row r="74" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="B74" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
       <c r="K74" s="8" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="L74" s="9"/>
       <c r="M74" s="10"/>
@@ -5084,35 +5181,35 @@
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="B75" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="I75" s="8"/>
       <c r="J75" s="8" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="L75" s="9"/>
       <c r="M75" s="10"/>
@@ -5122,33 +5219,33 @@
     </row>
     <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="B76" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
       <c r="K76" s="8" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="L76" s="9"/>
       <c r="M76" s="10"/>
@@ -5158,31 +5255,31 @@
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="B77" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
@@ -5194,28 +5291,28 @@
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="B78" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="8"/>
@@ -5228,35 +5325,35 @@
     </row>
     <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="B79" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="L79" s="9"/>
       <c r="M79" s="10"/>
@@ -5266,31 +5363,31 @@
     </row>
     <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B80" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
@@ -5302,33 +5399,33 @@
     </row>
     <row r="81" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="B81" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="8"/>
       <c r="K81" s="8" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
       <c r="L81" s="9"/>
       <c r="M81" s="10"/>
@@ -5338,31 +5435,31 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="B82" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
@@ -5374,33 +5471,33 @@
     </row>
     <row r="83" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="B83" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="8"/>
       <c r="K83" s="8" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="L83" s="9"/>
       <c r="M83" s="10"/>
@@ -5410,37 +5507,37 @@
     </row>
     <row r="84" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="B84" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="L84" s="9"/>
       <c r="M84" s="10"/>
@@ -5450,28 +5547,28 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="I85" s="8"/>
       <c r="J85" s="8"/>
@@ -5484,31 +5581,31 @@
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B86" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
@@ -5520,28 +5617,28 @@
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="B87" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
@@ -5554,35 +5651,35 @@
     </row>
     <row r="88" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="B88" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="I88" s="8"/>
       <c r="J88" s="8" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="L88" s="9"/>
       <c r="M88" s="10"/>
@@ -5592,33 +5689,33 @@
     </row>
     <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="B89" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="I89" s="8"/>
       <c r="J89" s="8"/>
       <c r="K89" s="8" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="L89" s="9"/>
       <c r="M89" s="10"/>
@@ -5628,31 +5725,31 @@
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="B90" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
@@ -5664,28 +5761,28 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B91" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I91" s="8"/>
       <c r="J91" s="8"/>
@@ -5698,28 +5795,28 @@
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B92" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
@@ -5732,28 +5829,28 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="B93" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
@@ -5766,28 +5863,28 @@
     </row>
     <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="B94" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
@@ -5800,28 +5897,28 @@
     </row>
     <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="B95" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="8"/>
@@ -5834,28 +5931,28 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="B96" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
@@ -5868,28 +5965,28 @@
     </row>
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="B97" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
@@ -5902,33 +5999,33 @@
     </row>
     <row r="98" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="B98" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="I98" s="8"/>
       <c r="J98" s="8"/>
       <c r="K98" s="8" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="L98" s="9"/>
       <c r="M98" s="10"/>
@@ -5938,33 +6035,33 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="B99" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
       <c r="K99" s="8" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="L99" s="9"/>
       <c r="M99" s="10"/>
@@ -5974,37 +6071,37 @@
     </row>
     <row r="100" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="B100" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="L100" s="9"/>
       <c r="M100" s="10"/>
@@ -6014,37 +6111,37 @@
     </row>
     <row r="101" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="B101" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="L101" s="9"/>
       <c r="M101" s="10"/>
@@ -6054,33 +6151,33 @@
     </row>
     <row r="102" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="B102" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="I102" s="8"/>
       <c r="J102" s="8"/>
       <c r="K102" s="8" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L102" s="9"/>
       <c r="M102" s="10"/>
@@ -6090,28 +6187,28 @@
     </row>
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="B103" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
@@ -6124,28 +6221,28 @@
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="B104" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
@@ -6158,28 +6255,28 @@
     </row>
     <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="B105" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
@@ -6192,28 +6289,28 @@
     </row>
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="B106" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
@@ -6226,28 +6323,28 @@
     </row>
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="B107" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
@@ -6260,31 +6357,31 @@
     </row>
     <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="B108" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
@@ -6296,34 +6393,34 @@
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="B109" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="K109" s="8"/>
       <c r="L109" s="9"/>
@@ -6334,28 +6431,28 @@
     </row>
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="B110" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
@@ -6368,28 +6465,28 @@
     </row>
     <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="B111" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
@@ -6402,28 +6499,28 @@
     </row>
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="B112" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="8"/>
@@ -6473,31 +6570,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>557</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6505,7 +6602,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C2" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A2)</f>
@@ -6541,7 +6638,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C3" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A3)</f>
@@ -6577,7 +6674,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C4" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A4)</f>
@@ -6613,7 +6710,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A5)</f>
@@ -6649,7 +6746,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A6)</f>
@@ -6685,7 +6782,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A7)</f>
@@ -6721,7 +6818,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A8)</f>
@@ -6757,7 +6854,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A9)</f>
@@ -6793,7 +6890,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A10)</f>
@@ -6829,7 +6926,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C11" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A11)</f>
@@ -6865,7 +6962,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C12" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A12)</f>
@@ -6901,7 +6998,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A13)</f>
@@ -6937,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C14" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A14)</f>
@@ -6973,7 +7070,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A15)</f>
@@ -7009,7 +7106,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A16)</f>
@@ -7045,7 +7142,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="C17" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A17)</f>
@@ -7081,7 +7178,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A18)</f>
@@ -7117,7 +7214,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="C19" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A19)</f>
@@ -7153,7 +7250,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="C20" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A20)</f>
@@ -7189,7 +7286,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A21)</f>
@@ -7225,7 +7322,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A22)</f>
@@ -7261,7 +7358,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A23)</f>
@@ -7295,7 +7392,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13"/>
       <c r="B24" s="14" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">SUM(C2:C23)</f>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="591">
   <si>
     <t xml:space="preserve">ΚΥΑ 1689/2025 και Microsoft 365: checklist συμμόρφωσης</t>
   </si>
@@ -207,10 +207,13 @@
     <t xml:space="preserve">Ολοκληρωμένο πρόγραμμα διαχείρισης κινδύνων κυβερνοασφάλειας, με ευθύνη του ανώτατου οργάνου διοίκησης.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Purview Compliance Manager (assessment «NIS 2 Directive») ως μητρώο του προγράμματος. Microsoft Secure Score ως μετρήσιμη τεχνική βάση.</t>
+    <t xml:space="preserve">Microsoft Purview Compliance Manager (assessment «NIS2 Directive (EU) 2022/2555») ως μητρώο του προγράμματος. Microsoft Secure Score ως μετρήσιμη τεχνική βάση.</t>
   </si>
   <si>
     <t xml:space="preserve">Απόφαση/πρακτικό ΔΣ για το πρόγραμμα. Compliance Manager: βαθμολογία και κατάσταση improvement actions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium regulation του Compliance Manager για το NIS 2 (αγοράζεται ξεχωριστά, ή ως ένα από τα τρία δωρεάν premium regulations με Microsoft 365 E5)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
@@ -229,6 +232,9 @@
     <t xml:space="preserve">Πρακτικά ΔΣ, εγκεκριμένος προϋπολογισμός, βεβαιώσεις εκπαίδευσης μελών ΔΣ.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Office 365 Plan 2 (Attack simulation training)</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.1.α</t>
   </si>
   <si>
@@ -244,6 +250,9 @@
     <t xml:space="preserve">Εγκεκριμένη μεθοδολογία διαχείρισης κινδύνων.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο)</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.1.β</t>
   </si>
   <si>
@@ -254,6 +263,9 @@
   </si>
   <si>
     <t xml:space="preserve">Μητρώο κινδύνων. Secure Score: History και τάση βαθμολογίας.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 ή Microsoft Defender Vulnerability Management standalone</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
@@ -306,7 +318,7 @@
     <t xml:space="preserve">Defender portal: Threat analytics, Vulnerability management (Weaknesses, Recommendations).</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender XDR (Microsoft 365 E5 ή αντίστοιχο)</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (περιλαμβάνεται στο Microsoft 365 E5). Εναλλακτικά Microsoft Defender Vulnerability Management standalone για την αξιολόγηση ευπαθειών.</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/previews/vulnerability-remediation-agent-intune/
@@ -452,12 +464,15 @@
     <t xml:space="preserve">Διαδικασίες παρακολούθησης της συμμόρφωσης με τις κανονιστικές υποχρεώσεις και περιοδική αναφορά στο ανώτατο όργανο.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Purview Compliance Manager με τα assessments «NIS 2 Directive» και «ISO/IEC 27001:2022», συνδεδεμένα με το Secure Score.</t>
+    <t xml:space="preserve">Microsoft Purview Compliance Manager με τα assessments «NIS2 Directive (EU) 2022/2555» και «ISO/IEC 27001:2022», συνδεδεμένα με το Secure Score.</t>
   </si>
   <si>
     <t xml:space="preserve">Compliance Manager: assessment score και εξαγωγή αναφοράς. Αναφορά προς το ΔΣ.</t>
   </si>
   <si>
+    <t xml:space="preserve">Premium regulations του Compliance Manager για NIS 2 και ISO/IEC 27001:2022 (αγοράζονται ξεχωριστά, ή ως δύο από τα τρία δωρεάν premium regulations με Microsoft 365 E5)</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.β</t>
   </si>
   <si>
@@ -536,7 +551,7 @@
     <t xml:space="preserve">Defender portal: Assets, Devices. Intune: Devices. Εξαγωγές καταλόγου.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender for IoT (για τα αγαθά OT)</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 ή Microsoft Defender Vulnerability Management standalone (software inventory, πλήρες device inventory). Microsoft Defender for IoT (για τα αγαθά OT).</t>
   </si>
   <si>
     <t xml:space="preserve">Ο ορισμός ιδιοκτήτη (owner) ανά αγαθό δεν καλύπτεται από προϊόντα Microsoft. Τηρείται σε ξεχωριστό μητρώο αγαθών.</t>
@@ -559,6 +574,9 @@
     <t xml:space="preserve">Purview portal: Information protection, Labels και Label policies. Content explorer.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft 365 E5 ή Microsoft Purview Suite (auto-labeling και Content explorer). Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο)</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/</t>
   </si>
   <si>
@@ -642,6 +660,9 @@
     <t xml:space="preserve">Υπογεγραμμένες συμβάσεις. Entra admin center: External Identities, Cross-tenant access settings.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Entra ID Governance ή Microsoft Entra ID P2 (access reviews)</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/generally-available/cross-tenant-message-recall-exchange-online/
 https://thecybersec.gr/posts/entra-tenant-governance-ga/</t>
   </si>
@@ -728,7 +749,7 @@
     <t xml:space="preserve">Role assignments, group memberships, αποτελέσματα access reviews.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID Governance (access reviews και entitlement management)</t>
+    <t xml:space="preserve">Microsoft Entra ID Governance ή Microsoft Entra ID P2 (access reviews και entitlement management)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/previews/ad-group-enforcement-cloud-sync/
@@ -795,6 +816,9 @@
   </si>
   <si>
     <t xml:space="preserve">Conditional Access policies. Sign-in logs: authentication requirement. Secure Score: MFA recommendations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Entra ID P2 (Microsoft Entra ID Protection, για policies με βάση sign-in risk ή user risk)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
@@ -814,7 +838,7 @@
     <t xml:space="preserve">Ιστορικό αλλαγών Conditional Access (audit logs), αποτελέσματα access reviews.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID Governance ή Microsoft Entra ID P2 (access reviews)</t>
+    <t xml:space="preserve">Το Conditional Access insights and reporting χρειάζεται Log Analytics workspace (συνδρομή Azure) με τα sign-in logs του Entra.</t>
   </si>
   <si>
     <t xml:space="preserve">14.α</t>
@@ -826,7 +850,7 @@
     <t xml:space="preserve">Διαδικασίες και εργαλεία για την επιβολή ρυθμίσεων και παραμετροποιήσεων σε υλικό, λογισμικό, υπηρεσίες και δίκτυο.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Intune: configuration profiles, compliance policies, security baselines. Tenant configuration management στο Microsoft Entra για τις ρυθμίσεις του tenant.</t>
+    <t xml:space="preserve">Microsoft Intune: configuration profiles, compliance policies, security baselines. Configuration management στο Microsoft Entra Tenant Governance (baselines, drift detection, snapshots) για τις ρυθμίσεις του tenant σε Entra, Intune, Exchange Online, Teams, Purview και Defender.</t>
   </si>
   <si>
     <t xml:space="preserve">Intune: Devices, Configuration και Compliance, per-policy device status.</t>
@@ -902,6 +926,9 @@
     <t xml:space="preserve">Προδιαγραφές ασφάλειας εφαρμογών.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Cloud Apps (το Microsoft 365 E3 περιλαμβάνει μόνο το Cloud App Discovery)</t>
+  </si>
+  <si>
     <t xml:space="preserve">15.β</t>
   </si>
   <si>
@@ -991,6 +1018,9 @@
     <t xml:space="preserve">Διαδικασία διαχείρισης ευπαθειών. Defender portal: Vulnerability management, Remediation.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το Defender Vulnerability Management</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/previews/vulnerability-remediation-agent-intune/</t>
   </si>
   <si>
@@ -1004,6 +1034,9 @@
   </si>
   <si>
     <t xml:space="preserve">Defender portal: Weaknesses, Threat analytics. Αρχείο ενημερώσεων από CSIRT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το Defender Vulnerability Management και το Threat analytics</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/previews/vulnerability-remediation-agent-intune/
@@ -1020,6 +1053,9 @@
   </si>
   <si>
     <t xml:space="preserve">Intune: Windows update reports. Defender portal: Remediation, Exceptions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για τα exceptions στο Defender Vulnerability Management</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-client-windows-update-auto-upgrade/
@@ -1054,7 +1090,7 @@
     <t xml:space="preserve">Defender portal: Vulnerability management dashboard και εξαγωγή αναφοράς.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender External Attack Surface Management, Microsoft Defender for IoT</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το Defender Vulnerability Management, Microsoft Defender External Attack Surface Management, Microsoft Defender for IoT</t>
   </si>
   <si>
     <t xml:space="preserve">Το Defender Vulnerability Management καλύπτει τις συσκευές που έχουν γίνει onboarding. Ο δικτυακός εξοπλισμός χρειάζεται άλλο εργαλείο σάρωσης.</t>
@@ -1151,6 +1187,9 @@
     <t xml:space="preserve">Όσα ευρήματα αφορούν το Active Directory και τις ταυτότητες παρακολουθούνται στα security posture assessments του Microsoft Defender for Identity και στο Secure Score.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Identity (Microsoft 365 E5 ή αντίστοιχο)</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/generally-available/investigate-ad-domain-defender-identity/
 https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
   </si>
@@ -1179,7 +1218,7 @@
     <t xml:space="preserve">Ρυθμίσεις firewall. Intune: Endpoint security, Firewall. Global Secure Access: security profiles.</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure Firewall, Azure WAF (μόνο για workloads σε Azure)</t>
+    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone). Azure Firewall, Azure WAF (μόνο για workloads σε Azure)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-3-internet-access-profile/
@@ -1196,6 +1235,9 @@
   </si>
   <si>
     <t xml:space="preserve">Conditional Access policies με Global Secure Access. Traffic logs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Entra Private Access (Microsoft Entra Suite ή standalone)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
@@ -1270,6 +1312,9 @@
     <t xml:space="preserve">Αποτελέσματα port scanning. Secure Score recommendations. Intune: Firewall policies.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για τον εντοπισμό internet-facing συσκευών</t>
+  </si>
+  <si>
     <t xml:space="preserve">Οι ανοικτές θύρες στον δικτυακό εξοπλισμό δεν καλύπτονται από το Microsoft 365.</t>
   </si>
   <si>
@@ -1286,6 +1331,9 @@
   </si>
   <si>
     <t xml:space="preserve">DNS records (SPF, DKIM, DMARC). Global Secure Access: filtering policies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-3-internet-access-profile/
@@ -1348,7 +1396,7 @@
     <t xml:space="preserve">Intune: App Control policies, ASR rules report. Defender portal: Software inventory.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Defender Vulnerability Management (add-on ή standalone) για το block vulnerable applications</t>
+    <t xml:space="preserve">Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο) για το software inventory. Microsoft Defender Vulnerability Management (add-on ή standalone) για το block vulnerable applications</t>
   </si>
   <si>
     <t xml:space="preserve">20.γ</t>
@@ -1492,6 +1540,9 @@
     <t xml:space="preserve">Ρυθμίσεις connectors στο Exchange Online. Mail flow rules για κρυπτογράφηση.</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Entra Internet Access ή Microsoft Entra Private Access (Microsoft Entra Suite ή standalone)</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-2-microsoft-traffic-profile/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-4-private-access-profile/</t>
   </si>
@@ -1508,7 +1559,7 @@
     <t xml:space="preserve">Διαδικασία διαχείρισης κλειδιών. Intune: certificate profiles.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Cloud PKI (πρόσθετο του Intune), Customer Key (Microsoft 365 E5)</t>
+    <t xml:space="preserve">Microsoft Cloud PKI (περιλαμβάνεται στο Microsoft 365 E5, αλλιώς πρόσθετο του Intune), Customer Key (Microsoft 365 E5)</t>
   </si>
   <si>
     <t xml:space="preserve">22.ε</t>
@@ -1590,6 +1641,9 @@
   </si>
   <si>
     <t xml:space="preserve">Εγκεκριμένη πολιτική και πλάνο. Defender portal: Incidents, Action center.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender XDR (Microsoft 365 E5 ή αντίστοιχο) για το automated investigation and response και τα response actions ταυτοτήτων</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
@@ -1621,7 +1675,7 @@
     <t xml:space="preserve">Purview: Audit. Entra: Sign-in logs, Audit logs. Defender for Identity: sensor health.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Sentinel (για logs εκτός Microsoft 365)</t>
+    <t xml:space="preserve">Microsoft Defender for Identity και Microsoft Defender for Endpoint Plan 2 (Microsoft 365 E5 ή αντίστοιχο), Microsoft Entra ID P2 (Privileged Identity Management), Microsoft Sentinel (για logs εκτός Microsoft 365)</t>
   </si>
   <si>
     <t xml:space="preserve">Οι δικτυακές συσκευές χρειάζονται συλλογή logs εκτός Microsoft 365, π.χ. με Microsoft Sentinel ή άλλο SIEM.</t>
@@ -1661,6 +1715,9 @@
   </si>
   <si>
     <t xml:space="preserve">Defender portal: Incidents, Custom detection rules, Alert tuning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Defender XDR (Microsoft 365 E5 ή αντίστοιχο) για advanced hunting, custom detection rules, Defender for Cloud Apps και Defender for Identity</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
@@ -2598,10 +2655,12 @@
       <c r="H2" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="8"/>
+      <c r="I2" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="J2" s="8"/>
       <c r="K2" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="10"/>
@@ -2611,7 +2670,7 @@
     </row>
     <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>4</v>
@@ -2623,21 +2682,23 @@
         <v>58</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="8"/>
+        <v>67</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="J3" s="8"/>
       <c r="K3" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="10"/>
@@ -2647,30 +2708,32 @@
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="8"/>
+        <v>73</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="J4" s="8"/>
       <c r="K4" s="8"/>
       <c r="L4" s="9"/>
@@ -2681,33 +2744,35 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I5" s="8"/>
+        <v>78</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="J5" s="8"/>
       <c r="K5" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="10"/>
@@ -2717,33 +2782,33 @@
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="10"/>
@@ -2753,33 +2818,33 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B7" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L7" s="9"/>
       <c r="M7" s="10"/>
@@ -2787,37 +2852,37 @@
       <c r="O7" s="11"/>
       <c r="P7" s="10"/>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B8" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L8" s="9"/>
       <c r="M8" s="10"/>
@@ -2827,28 +2892,28 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B9" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
@@ -2861,28 +2926,28 @@
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
@@ -2895,28 +2960,28 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
@@ -2929,33 +2994,33 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="10"/>
@@ -2965,28 +3030,28 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
@@ -2999,31 +3064,31 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>7</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
@@ -3035,33 +3100,33 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
       <c r="K15" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L15" s="9"/>
       <c r="M15" s="10"/>
@@ -3071,28 +3136,28 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
@@ -3105,33 +3170,33 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B17" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
       <c r="K17" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L17" s="9"/>
       <c r="M17" s="10"/>
@@ -3141,28 +3206,28 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>8</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="8"/>
@@ -3173,35 +3238,37 @@
       <c r="O18" s="11"/>
       <c r="P18" s="10"/>
     </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B19" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="I19" s="8"/>
+        <v>145</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>146</v>
+      </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L19" s="9"/>
       <c r="M19" s="10"/>
@@ -3211,33 +3278,33 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B20" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L20" s="9"/>
       <c r="M20" s="10"/>
@@ -3247,33 +3314,33 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>9</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="10"/>
@@ -3283,28 +3350,28 @@
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
@@ -3317,28 +3384,28 @@
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
@@ -3351,28 +3418,28 @@
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B24" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
@@ -3385,28 +3452,28 @@
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B25" s="7" t="n">
         <v>10</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
@@ -3419,37 +3486,37 @@
     </row>
     <row r="26" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L26" s="9"/>
       <c r="M26" s="10"/>
@@ -3459,33 +3526,35 @@
     </row>
     <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="I27" s="8"/>
+        <v>179</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>180</v>
+      </c>
       <c r="J27" s="8"/>
       <c r="K27" s="8" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L27" s="9"/>
       <c r="M27" s="10"/>
@@ -3495,33 +3564,33 @@
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
       <c r="K28" s="8" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="L28" s="9"/>
       <c r="M28" s="10"/>
@@ -3531,28 +3600,28 @@
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B29" s="7" t="n">
         <v>11</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="8"/>
@@ -3565,28 +3634,28 @@
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
@@ -3599,33 +3668,33 @@
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="8"/>
       <c r="K31" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L31" s="9"/>
       <c r="M31" s="10"/>
@@ -3635,33 +3704,33 @@
     </row>
     <row r="32" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
       <c r="K32" s="8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L32" s="9"/>
       <c r="M32" s="10"/>
@@ -3671,33 +3740,35 @@
     </row>
     <row r="33" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B33" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="I33" s="8"/>
+        <v>207</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>208</v>
+      </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="L33" s="9"/>
       <c r="M33" s="10"/>
@@ -3707,28 +3778,28 @@
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B34" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
@@ -3741,33 +3812,33 @@
     </row>
     <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B35" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="8"/>
       <c r="K35" s="8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="L35" s="9"/>
       <c r="M35" s="10"/>
@@ -3777,28 +3848,28 @@
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>12</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
@@ -3811,33 +3882,33 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B37" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="L37" s="9"/>
       <c r="M37" s="10"/>
@@ -3847,33 +3918,33 @@
     </row>
     <row r="38" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B38" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="L38" s="9"/>
       <c r="M38" s="10"/>
@@ -3883,35 +3954,35 @@
     </row>
     <row r="39" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B39" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="L39" s="9"/>
       <c r="M39" s="10"/>
@@ -3921,35 +3992,35 @@
     </row>
     <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="J40" s="8"/>
       <c r="K40" s="8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="L40" s="9"/>
       <c r="M40" s="10"/>
@@ -3959,31 +4030,31 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B41" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
@@ -3995,33 +4066,33 @@
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="L42" s="9"/>
       <c r="M42" s="10"/>
@@ -4031,33 +4102,35 @@
     </row>
     <row r="43" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B43" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="I43" s="8"/>
+        <v>257</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>258</v>
+      </c>
       <c r="J43" s="8"/>
       <c r="K43" s="8" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="L43" s="9"/>
       <c r="M43" s="10"/>
@@ -4065,37 +4138,39 @@
       <c r="O43" s="11"/>
       <c r="P43" s="10"/>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B44" s="7" t="n">
         <v>13</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="J44" s="8"/>
+        <v>208</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>264</v>
+      </c>
       <c r="K44" s="8" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="L44" s="9"/>
       <c r="M44" s="10"/>
@@ -4103,35 +4178,35 @@
       <c r="O44" s="11"/>
       <c r="P44" s="10"/>
     </row>
-    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B45" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="L45" s="9"/>
       <c r="M45" s="10"/>
@@ -4141,35 +4216,35 @@
     </row>
     <row r="46" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B46" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="J46" s="8"/>
       <c r="K46" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="L46" s="9"/>
       <c r="M46" s="10"/>
@@ -4179,35 +4254,35 @@
     </row>
     <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B47" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="L47" s="9"/>
       <c r="M47" s="10"/>
@@ -4217,33 +4292,33 @@
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B48" s="7" t="n">
         <v>14</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L48" s="9"/>
       <c r="M48" s="10"/>
@@ -4253,30 +4328,32 @@
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B49" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="I49" s="8"/>
+        <v>291</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>292</v>
+      </c>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="9"/>
@@ -4287,35 +4364,35 @@
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B50" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="J50" s="8"/>
       <c r="K50" s="8" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="L50" s="9"/>
       <c r="M50" s="10"/>
@@ -4325,31 +4402,31 @@
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B51" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
@@ -4361,31 +4438,31 @@
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B52" s="7" t="n">
         <v>15</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="J52" s="8"/>
       <c r="K52" s="8"/>
@@ -4397,33 +4474,33 @@
     </row>
     <row r="53" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B53" s="7" t="n">
         <v>16</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L53" s="9"/>
       <c r="M53" s="10"/>
@@ -4433,28 +4510,28 @@
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B54" s="7" t="n">
         <v>16</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
@@ -4465,35 +4542,37 @@
       <c r="O54" s="11"/>
       <c r="P54" s="10"/>
     </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B55" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="I55" s="8"/>
+        <v>321</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>322</v>
+      </c>
       <c r="J55" s="8"/>
       <c r="K55" s="8" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="L55" s="9"/>
       <c r="M55" s="10"/>
@@ -4503,33 +4582,35 @@
     </row>
     <row r="56" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B56" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="I56" s="8"/>
+        <v>327</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>328</v>
+      </c>
       <c r="J56" s="8"/>
       <c r="K56" s="8" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="L56" s="9"/>
       <c r="M56" s="10"/>
@@ -4539,33 +4620,35 @@
     </row>
     <row r="57" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B57" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="I57" s="8"/>
+        <v>333</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>334</v>
+      </c>
       <c r="J57" s="8"/>
       <c r="K57" s="8" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="L57" s="9"/>
       <c r="M57" s="10"/>
@@ -4575,33 +4658,33 @@
     </row>
     <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B58" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
       <c r="K58" s="8" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="L58" s="9"/>
       <c r="M58" s="10"/>
@@ -4609,39 +4692,39 @@
       <c r="O58" s="11"/>
       <c r="P58" s="10"/>
     </row>
-    <row r="59" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B59" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="J59" s="8" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="L59" s="9"/>
       <c r="M59" s="10"/>
@@ -4651,33 +4734,35 @@
     </row>
     <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B60" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="I60" s="8"/>
+        <v>350</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>322</v>
+      </c>
       <c r="J60" s="8"/>
       <c r="K60" s="8" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="L60" s="9"/>
       <c r="M60" s="10"/>
@@ -4687,28 +4772,28 @@
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B61" s="7" t="n">
         <v>17</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
@@ -4721,28 +4806,28 @@
     </row>
     <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B62" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
@@ -4755,28 +4840,28 @@
     </row>
     <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B63" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
@@ -4789,33 +4874,35 @@
     </row>
     <row r="64" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="B64" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="I64" s="8"/>
+        <v>366</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>322</v>
+      </c>
       <c r="J64" s="8"/>
       <c r="K64" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L64" s="9"/>
       <c r="M64" s="10"/>
@@ -4825,33 +4912,33 @@
     </row>
     <row r="65" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B65" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
       <c r="K65" s="8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="L65" s="9"/>
       <c r="M65" s="10"/>
@@ -4861,28 +4948,28 @@
     </row>
     <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B66" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
@@ -4895,33 +4982,35 @@
     </row>
     <row r="67" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B67" s="7" t="n">
         <v>18</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="I67" s="8"/>
+        <v>366</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>377</v>
+      </c>
       <c r="J67" s="8"/>
       <c r="K67" s="8" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="L67" s="9"/>
       <c r="M67" s="10"/>
@@ -4931,28 +5020,28 @@
     </row>
     <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="B68" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
@@ -4965,35 +5054,35 @@
     </row>
     <row r="69" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="B69" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="8" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="L69" s="9"/>
       <c r="M69" s="10"/>
@@ -5003,33 +5092,35 @@
     </row>
     <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B70" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="I70" s="8"/>
+        <v>392</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>393</v>
+      </c>
       <c r="J70" s="8"/>
       <c r="K70" s="8" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="L70" s="9"/>
       <c r="M70" s="10"/>
@@ -5039,33 +5130,33 @@
     </row>
     <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B71" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="L71" s="9"/>
       <c r="M71" s="10"/>
@@ -5075,33 +5166,35 @@
     </row>
     <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B72" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="I72" s="8"/>
+        <v>402</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>393</v>
+      </c>
       <c r="J72" s="8"/>
       <c r="K72" s="8" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="L72" s="9"/>
       <c r="M72" s="10"/>
@@ -5111,28 +5204,28 @@
     </row>
     <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="B73" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="I73" s="8"/>
       <c r="J73" s="8"/>
@@ -5145,33 +5238,35 @@
     </row>
     <row r="74" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="B74" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="I74" s="8"/>
+        <v>411</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>393</v>
+      </c>
       <c r="J74" s="8"/>
       <c r="K74" s="8" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="L74" s="9"/>
       <c r="M74" s="10"/>
@@ -5181,35 +5276,37 @@
     </row>
     <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="B75" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="I75" s="8"/>
+        <v>416</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>417</v>
+      </c>
       <c r="J75" s="8" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="K75" s="8" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="L75" s="9"/>
       <c r="M75" s="10"/>
@@ -5219,33 +5316,35 @@
     </row>
     <row r="76" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="B76" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="I76" s="8"/>
+        <v>423</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>424</v>
+      </c>
       <c r="J76" s="8"/>
       <c r="K76" s="8" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="L76" s="9"/>
       <c r="M76" s="10"/>
@@ -5255,31 +5354,31 @@
     </row>
     <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="B77" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
@@ -5291,28 +5390,28 @@
     </row>
     <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="B78" s="7" t="n">
         <v>19</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="8"/>
@@ -5325,35 +5424,35 @@
     </row>
     <row r="79" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="B79" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="8" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="K79" s="8" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="L79" s="9"/>
       <c r="M79" s="10"/>
@@ -5361,33 +5460,33 @@
       <c r="O79" s="11"/>
       <c r="P79" s="10"/>
     </row>
-    <row r="80" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="B80" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
@@ -5399,33 +5498,33 @@
     </row>
     <row r="81" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B81" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="8"/>
       <c r="K81" s="8" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="L81" s="9"/>
       <c r="M81" s="10"/>
@@ -5435,31 +5534,31 @@
     </row>
     <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="B82" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
@@ -5471,33 +5570,35 @@
     </row>
     <row r="83" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="B83" s="7" t="n">
         <v>20</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="I83" s="8"/>
+        <v>458</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>424</v>
+      </c>
       <c r="J83" s="8"/>
       <c r="K83" s="8" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="L83" s="9"/>
       <c r="M83" s="10"/>
@@ -5507,37 +5608,37 @@
     </row>
     <row r="84" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="B84" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="K84" s="8" t="s">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="L84" s="9"/>
       <c r="M84" s="10"/>
@@ -5547,28 +5648,28 @@
     </row>
     <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="B85" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="F85" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="I85" s="8"/>
       <c r="J85" s="8"/>
@@ -5581,31 +5682,31 @@
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="B86" s="7" t="n">
         <v>21</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
@@ -5617,28 +5718,28 @@
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7" t="s">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="B87" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="8"/>
@@ -5651,35 +5752,35 @@
     </row>
     <row r="88" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="B88" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="I88" s="8"/>
       <c r="J88" s="8" t="s">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="K88" s="8" t="s">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="L88" s="9"/>
       <c r="M88" s="10"/>
@@ -5689,33 +5790,35 @@
     </row>
     <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="B89" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="I89" s="8"/>
+        <v>489</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>490</v>
+      </c>
       <c r="J89" s="8"/>
       <c r="K89" s="8" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="L89" s="9"/>
       <c r="M89" s="10"/>
@@ -5725,31 +5828,31 @@
     </row>
     <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="B90" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
@@ -5761,28 +5864,28 @@
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="B91" s="7" t="n">
         <v>22</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I91" s="8"/>
       <c r="J91" s="8"/>
@@ -5795,28 +5898,28 @@
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="B92" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="8"/>
@@ -5829,28 +5932,28 @@
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="B93" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="F93" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="8"/>
@@ -5863,28 +5966,28 @@
     </row>
     <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="B94" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="8"/>
@@ -5897,28 +6000,28 @@
     </row>
     <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="B95" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="8"/>
@@ -5931,28 +6034,28 @@
     </row>
     <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="B96" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="8"/>
@@ -5965,28 +6068,28 @@
     </row>
     <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="B97" s="7" t="n">
         <v>23</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I97" s="8"/>
       <c r="J97" s="8"/>
@@ -5999,33 +6102,35 @@
     </row>
     <row r="98" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="B98" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="I98" s="8"/>
+        <v>523</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>524</v>
+      </c>
       <c r="J98" s="8"/>
       <c r="K98" s="8" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="L98" s="9"/>
       <c r="M98" s="10"/>
@@ -6035,33 +6140,33 @@
     </row>
     <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="B99" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
       <c r="K99" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L99" s="9"/>
       <c r="M99" s="10"/>
@@ -6071,37 +6176,37 @@
     </row>
     <row r="100" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="B100" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="K100" s="8" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="L100" s="9"/>
       <c r="M100" s="10"/>
@@ -6111,37 +6216,37 @@
     </row>
     <row r="101" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="B101" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="F101" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L101" s="9"/>
       <c r="M101" s="10"/>
@@ -6151,33 +6256,35 @@
     </row>
     <row r="102" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="B102" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="I102" s="8"/>
+        <v>546</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>547</v>
+      </c>
       <c r="J102" s="8"/>
       <c r="K102" s="8" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="L102" s="9"/>
       <c r="M102" s="10"/>
@@ -6187,28 +6294,28 @@
     </row>
     <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="B103" s="7" t="n">
         <v>24</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="I103" s="8"/>
       <c r="J103" s="8"/>
@@ -6221,28 +6328,28 @@
     </row>
     <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7" t="s">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="B104" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="I104" s="8"/>
       <c r="J104" s="8"/>
@@ -6255,28 +6362,28 @@
     </row>
     <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="B105" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="I105" s="8"/>
       <c r="J105" s="8"/>
@@ -6289,28 +6396,28 @@
     </row>
     <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="B106" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="I106" s="8"/>
       <c r="J106" s="8"/>
@@ -6323,28 +6430,28 @@
     </row>
     <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="B107" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="I107" s="8"/>
       <c r="J107" s="8"/>
@@ -6357,31 +6464,31 @@
     </row>
     <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7" t="s">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="B108" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
@@ -6393,34 +6500,34 @@
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="B109" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>36</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="J109" s="8" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="K109" s="8"/>
       <c r="L109" s="9"/>
@@ -6431,28 +6538,28 @@
     </row>
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="B110" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>58</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="I110" s="8"/>
       <c r="J110" s="8"/>
@@ -6465,28 +6572,28 @@
     </row>
     <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="B111" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="8"/>
@@ -6499,28 +6606,28 @@
     </row>
     <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="B112" s="7" t="n">
         <v>25</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="8"/>
@@ -6576,22 +6683,22 @@
         <v>44</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>31</v>
@@ -6638,7 +6745,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A3)</f>
@@ -6674,7 +6781,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C4" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A4)</f>
@@ -6710,7 +6817,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A5)</f>
@@ -6746,7 +6853,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A6)</f>
@@ -6782,7 +6889,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A7)</f>
@@ -6818,7 +6925,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A8)</f>
@@ -6854,7 +6961,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A9)</f>
@@ -6890,7 +6997,7 @@
         <v>12</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A10)</f>
@@ -6926,7 +7033,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C11" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A11)</f>
@@ -6962,7 +7069,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C12" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A12)</f>
@@ -6998,7 +7105,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A13)</f>
@@ -7034,7 +7141,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C14" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A14)</f>
@@ -7070,7 +7177,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A15)</f>
@@ -7106,7 +7213,7 @@
         <v>18</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A16)</f>
@@ -7142,7 +7249,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="C17" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A17)</f>
@@ -7178,7 +7285,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A18)</f>
@@ -7214,7 +7321,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="C19" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A19)</f>
@@ -7250,7 +7357,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="C20" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A20)</f>
@@ -7286,7 +7393,7 @@
         <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A21)</f>
@@ -7322,7 +7429,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A22)</f>
@@ -7358,7 +7465,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">COUNTIF(Checklist!$B$2:$B$112,A23)</f>
@@ -7392,7 +7499,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13"/>
       <c r="B24" s="14" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">SUM(C2:C23)</f>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -787,7 +787,7 @@
     <t xml:space="preserve">Entra audit logs: account disabled, sessions revoked. Αρχείο αποχωρήσεων HR.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra ID Governance (lifecycle workflows)</t>
+    <t xml:space="preserve">Microsoft Entra ID Governance (lifecycle workflows· πρόσθετο, περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">13.στ</t>
@@ -1218,7 +1218,7 @@
     <t xml:space="preserve">Ρυθμίσεις firewall. Intune: Endpoint security, Firewall. Global Secure Access: security profiles.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone). Azure Firewall, Azure WAF (μόνο για workloads σε Azure)</t>
+    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7). Azure Firewall, Azure WAF (μόνο για workloads σε Azure)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-3-internet-access-profile/
@@ -1237,7 +1237,7 @@
     <t xml:space="preserve">Conditional Access policies με Global Secure Access. Traffic logs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra Private Access (Microsoft Entra Suite ή standalone)</t>
+    <t xml:space="preserve">Microsoft Entra Private Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
@@ -1333,7 +1333,7 @@
     <t xml:space="preserve">DNS records (SPF, DKIM, DMARC). Global Secure Access: filtering policies.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone)</t>
+    <t xml:space="preserve">Microsoft Entra Internet Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-3-internet-access-profile/
@@ -1540,7 +1540,7 @@
     <t xml:space="preserve">Ρυθμίσεις connectors στο Exchange Online. Mail flow rules για κρυπτογράφηση.</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Entra Internet Access ή Microsoft Entra Private Access (Microsoft Entra Suite ή standalone)</t>
+    <t xml:space="preserve">Microsoft Entra Internet Access ή Microsoft Entra Private Access (Microsoft Entra Suite ή standalone· περιλαμβάνεται στο Microsoft 365 E7)</t>
   </si>
   <si>
     <t xml:space="preserve">https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-2-microsoft-traffic-profile/
@@ -4028,7 +4028,7 @@
       <c r="O40" s="11"/>
       <c r="P40" s="10"/>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
         <v>244</v>
       </c>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -2315,7 +2315,8 @@
       <c r="J28" s="25" t="n"/>
       <c r="K28" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/</t>
+          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="L28" s="26" t="n"/>
@@ -3220,7 +3221,8 @@
       <c r="K45" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/entra-tenant-governance-ga/
-https://thecybersec.gr/posts/new-features/secure-score-ai-readiness-tpm-vbs-hvci-laps/</t>
+https://thecybersec.gr/posts/new-features/secure-score-ai-readiness-tpm-vbs-hvci-laps/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/</t>
         </is>
       </c>
       <c r="L45" s="26" t="n"/>
@@ -5052,7 +5054,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-oikogeneia-praktikos-odigos/
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="L79" s="26" t="n"/>
@@ -5108,7 +5111,8 @@
       <c r="J80" s="25" t="n"/>
       <c r="K80" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+          <t>https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
         </is>
       </c>
       <c r="L80" s="26" t="n"/>
@@ -6042,7 +6046,8 @@
         <is>
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/
-https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/</t>
+https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
         </is>
       </c>
       <c r="L98" s="26" t="n"/>
@@ -6157,7 +6162,8 @@
           <t>https://thecybersec.gr/posts/new-features/defender-for-identity-health-issue-missing-windows-events/
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
-https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/</t>
         </is>
       </c>
       <c r="L100" s="26" t="n"/>
@@ -6217,7 +6223,8 @@
       </c>
       <c r="K101" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
         </is>
       </c>
       <c r="L101" s="26" t="n"/>
@@ -6277,7 +6284,9 @@
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/
-https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/</t>
+https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
         </is>
       </c>
       <c r="L102" s="26" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>04/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,8 @@
       <c r="K3" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/</t>
+https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
+https://thecybersec.gr/tekmiriosi-ekpaideysis/</t>
         </is>
       </c>
       <c r="L3" s="26" t="n"/>
@@ -5167,7 +5168,10 @@
           <t>https://thecybersec.gr/posts/new-features/mdo-encrypted-attachment-protection-mc1440701/
 https://thecybersec.gr/posts/new-features/prompt-injection-protection-defender-office-365/
 https://thecybersec.gr/posts/generally-available/mdo-mark-and-notify-localization/
-https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/</t>
+https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
+https://thecybersec.gr/elegxos-domain/
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/</t>
         </is>
       </c>
       <c r="L81" s="26" t="n"/>
@@ -5338,7 +5342,11 @@
       <c r="K84" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/generally-available/mdo-mark-and-notify-localization/
-https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/</t>
+https://thecybersec.gr/posts/new-features/report-a-call-report-a-meeting-teams-security-reporting/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
+https://thecybersec.gr/tekmiriosi-ekpaideysis/
+https://thecybersec.gr/kouiz-phishing/</t>
         </is>
       </c>
       <c r="L84" s="26" t="n"/>
@@ -5388,7 +5396,11 @@
       </c>
       <c r="I85" s="25" t="n"/>
       <c r="J85" s="25" t="n"/>
-      <c r="K85" s="25" t="n"/>
+      <c r="K85" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/tekmiriosi-ekpaideysis/</t>
+        </is>
+      </c>
       <c r="L85" s="26" t="n"/>
       <c r="M85" s="27" t="n"/>
       <c r="N85" s="27" t="n"/>
@@ -5440,7 +5452,11 @@
         </is>
       </c>
       <c r="J86" s="25" t="n"/>
-      <c r="K86" s="25" t="n"/>
+      <c r="K86" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/tekmiriosi-ekpaideysis/</t>
+        </is>
+      </c>
       <c r="L86" s="26" t="n"/>
       <c r="M86" s="27" t="n"/>
       <c r="N86" s="27" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,8 @@
       <c r="K40" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="L40" s="26" t="n"/>
@@ -6179,7 +6180,8 @@
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
-https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/</t>
+https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="L100" s="26" t="n"/>
@@ -6302,7 +6304,8 @@
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
-https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
         </is>
       </c>
       <c r="L102" s="26" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -2208,7 +2208,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/microsoft-defender-oikogeneia-praktikos-odigos/
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="L26" s="26" t="n"/>
@@ -2317,7 +2318,8 @@
       <c r="K28" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
-https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="L28" s="26" t="n"/>
@@ -2519,7 +2521,8 @@
         <is>
           <t>https://thecybersec.gr/posts/allowed-agent-types-only-certified-external-publishers/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
-https://thecybersec.gr/posts/gsa-mcp-firewall/</t>
+https://thecybersec.gr/posts/gsa-mcp-firewall/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="L32" s="26" t="n"/>
@@ -2889,7 +2892,8 @@
       <c r="K39" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/previews/ad-group-enforcement-cloud-sync/
-https://thecybersec.gr/posts/entra-tenant-governance-ga/</t>
+https://thecybersec.gr/posts/entra-tenant-governance-ga/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="L39" s="26" t="n"/>
@@ -6305,7 +6309,8 @@
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
         </is>
       </c>
       <c r="L102" s="26" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -965,8 +965,9 @@
       <c r="J2" s="25" t="n"/>
       <c r="K2" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/</t>
+          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L2" s="26" t="n"/>
@@ -1345,7 +1346,11 @@
       </c>
       <c r="I9" s="25" t="n"/>
       <c r="J9" s="25" t="n"/>
-      <c r="K9" s="25" t="n"/>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L9" s="26" t="n"/>
       <c r="M9" s="27" t="n"/>
       <c r="N9" s="27" t="n"/>
@@ -1393,7 +1398,11 @@
       </c>
       <c r="I10" s="25" t="n"/>
       <c r="J10" s="25" t="n"/>
-      <c r="K10" s="25" t="n"/>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L10" s="26" t="n"/>
       <c r="M10" s="27" t="n"/>
       <c r="N10" s="27" t="n"/>
@@ -1441,7 +1450,11 @@
       </c>
       <c r="I11" s="25" t="n"/>
       <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L11" s="26" t="n"/>
       <c r="M11" s="27" t="n"/>
       <c r="N11" s="27" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -965,7 +965,7 @@
       <c r="J2" s="25" t="n"/>
       <c r="K2" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
 https://thecybersec.gr/mitroo-politikon/</t>
         </is>
@@ -6081,7 +6081,8 @@
           <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
-https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="L98" s="26" t="n"/>
@@ -6259,7 +6260,8 @@
       <c r="K101" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
-https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/</t>
+https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="L101" s="26" t="n"/>
@@ -6323,7 +6325,8 @@
 https://thecybersec.gr/posts/generally-available/defender-identity-sensor-v3-automatic-activation/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-identity-deep-dive/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
         </is>
       </c>
       <c r="L102" s="26" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>18/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,8 @@
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
 https://thecybersec.gr/posts/microsoft-secure-score-grc-programma-ciso/
-https://thecybersec.gr/tekmiriosi-ekpaideysis/</t>
+https://thecybersec.gr/tekmiriosi-ekpaideysis/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L3" s="26" t="n"/>
@@ -1079,7 +1080,11 @@
         </is>
       </c>
       <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L4" s="26" t="n"/>
       <c r="M4" s="27" t="n"/>
       <c r="N4" s="27" t="n"/>
@@ -1134,7 +1139,8 @@
       <c r="K5" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
-https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/</t>
+https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L5" s="26" t="n"/>
@@ -1187,7 +1193,8 @@
       <c r="K6" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
-https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-1-anatomy/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L6" s="26" t="n"/>
@@ -1504,7 +1511,8 @@
       <c r="J12" s="25" t="n"/>
       <c r="K12" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/</t>
+          <t>https://thecybersec.gr/posts/secure-score-defender-praktikos-odigos/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L12" s="26" t="n"/>
@@ -1657,7 +1665,8 @@
       <c r="K15" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L15" s="26" t="n"/>
@@ -1862,7 +1871,8 @@
       <c r="K19" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L19" s="26" t="n"/>
@@ -2016,7 +2026,11 @@
       </c>
       <c r="I22" s="25" t="n"/>
       <c r="J22" s="25" t="n"/>
-      <c r="K22" s="25" t="n"/>
+      <c r="K22" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L22" s="26" t="n"/>
       <c r="M22" s="27" t="n"/>
       <c r="N22" s="27" t="n"/>
@@ -2222,7 +2236,8 @@
 https://thecybersec.gr/posts/microsoft-defender-oikogeneia-praktikos-odigos/
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L26" s="26" t="n"/>
@@ -2278,7 +2293,8 @@
       <c r="J27" s="25" t="n"/>
       <c r="K27" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/</t>
+          <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L27" s="26" t="n"/>
@@ -2332,7 +2348,8 @@
         <is>
           <t>https://thecybersec.gr/posts/purview-autolabeling-500k-scale-increase/
 https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L28" s="26" t="n"/>
@@ -2382,7 +2399,11 @@
       </c>
       <c r="I29" s="25" t="n"/>
       <c r="J29" s="25" t="n"/>
-      <c r="K29" s="25" t="n"/>
+      <c r="K29" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L29" s="26" t="n"/>
       <c r="M29" s="27" t="n"/>
       <c r="N29" s="27" t="n"/>
@@ -2430,7 +2451,11 @@
       </c>
       <c r="I30" s="25" t="n"/>
       <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
+      <c r="K30" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L30" s="26" t="n"/>
       <c r="M30" s="27" t="n"/>
       <c r="N30" s="27" t="n"/>
@@ -2480,7 +2505,8 @@
       <c r="J31" s="25" t="n"/>
       <c r="K31" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/</t>
+          <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L31" s="26" t="n"/>
@@ -2535,7 +2561,8 @@
           <t>https://thecybersec.gr/posts/allowed-agent-types-only-certified-external-publishers/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/gsa-mcp-firewall/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-cloud-apps-deep-dive/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L32" s="26" t="n"/>
@@ -2794,7 +2821,8 @@
       <c r="J37" s="25" t="n"/>
       <c r="K37" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/</t>
+          <t>https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L37" s="26" t="n"/>
@@ -3301,7 +3329,8 @@
 https://thecybersec.gr/posts/secure-score-grc-part-2-ecosystem/
 https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
 https://thecybersec.gr/posts/new-features/secure-score-ai-readiness-tpm-vbs-hvci-laps/
-https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/</t>
+https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L46" s="26" t="n"/>
@@ -3463,7 +3492,11 @@
         </is>
       </c>
       <c r="J49" s="25" t="n"/>
-      <c r="K49" s="25" t="n"/>
+      <c r="K49" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L49" s="26" t="n"/>
       <c r="M49" s="27" t="n"/>
       <c r="N49" s="27" t="n"/>
@@ -3675,7 +3708,8 @@
         <is>
           <t>https://thecybersec.gr/posts/global-secure-access/global-secure-access-client-windows-update-auto-upgrade/
 https://thecybersec.gr/posts/entra-token-protection-bulk-enrollment-limitation/
-https://thecybersec.gr/posts/entra-connect-mandatory-upgrade-2026/</t>
+https://thecybersec.gr/posts/entra-connect-mandatory-upgrade-2026/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L53" s="26" t="n"/>
@@ -3779,7 +3813,8 @@
       <c r="J55" s="25" t="n"/>
       <c r="K55" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/previews/vulnerability-remediation-agent-intune/</t>
+          <t>https://thecybersec.gr/posts/previews/vulnerability-remediation-agent-intune/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L55" s="26" t="n"/>
@@ -4063,7 +4098,8 @@
       <c r="K60" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/previews/vulnerability-remediation-agent-intune/
-https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L60" s="26" t="n"/>
@@ -4161,7 +4197,11 @@
       </c>
       <c r="I62" s="25" t="n"/>
       <c r="J62" s="25" t="n"/>
-      <c r="K62" s="25" t="n"/>
+      <c r="K62" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L62" s="26" t="n"/>
       <c r="M62" s="27" t="n"/>
       <c r="N62" s="27" t="n"/>
@@ -4263,7 +4303,8 @@
       <c r="J64" s="25" t="n"/>
       <c r="K64" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
+          <t>https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L64" s="26" t="n"/>
@@ -4316,7 +4357,8 @@
       <c r="K65" s="25" t="inlineStr">
         <is>
           <t>https://thecybersec.gr/posts/secure-score-grc-part-0-intro/
-https://thecybersec.gr/posts/secure-score-grc-part-3-operations/</t>
+https://thecybersec.gr/posts/secure-score-grc-part-3-operations/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L65" s="26" t="n"/>
@@ -4471,7 +4513,11 @@
       </c>
       <c r="I68" s="25" t="n"/>
       <c r="J68" s="25" t="n"/>
-      <c r="K68" s="25" t="n"/>
+      <c r="K68" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L68" s="26" t="n"/>
       <c r="M68" s="27" t="n"/>
       <c r="N68" s="27" t="n"/>
@@ -5364,7 +5410,8 @@
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
 https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
 https://thecybersec.gr/tekmiriosi-ekpaideysis/
-https://thecybersec.gr/kouiz-phishing/</t>
+https://thecybersec.gr/kouiz-phishing/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L84" s="26" t="n"/>
@@ -5522,7 +5569,11 @@
       </c>
       <c r="I87" s="25" t="n"/>
       <c r="J87" s="25" t="n"/>
-      <c r="K87" s="25" t="n"/>
+      <c r="K87" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L87" s="26" t="n"/>
       <c r="M87" s="27" t="n"/>
       <c r="N87" s="27" t="n"/>
@@ -5784,7 +5835,11 @@
       </c>
       <c r="I92" s="25" t="n"/>
       <c r="J92" s="25" t="n"/>
-      <c r="K92" s="25" t="n"/>
+      <c r="K92" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L92" s="26" t="n"/>
       <c r="M92" s="27" t="n"/>
       <c r="N92" s="27" t="n"/>
@@ -6082,7 +6137,8 @@
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-response-actions-identity-accounts/
 https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
 https://thecybersec.gr/posts/previews/isoc-integrated-security-operations-defender/
-https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/</t>
+https://thecybersec.gr/posts/previews/isoc-sentinel-defender-xdr-poio-epilegeis/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L98" s="26" t="n"/>
@@ -6134,7 +6190,8 @@
       <c r="J99" s="25" t="n"/>
       <c r="K99" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/</t>
+          <t>https://thecybersec.gr/posts/microsoft-defender-xdr-full-tutorial-ciso/
+https://thecybersec.gr/mitroo-politikon/</t>
         </is>
       </c>
       <c r="L99" s="26" t="n"/>
@@ -6424,7 +6481,11 @@
       </c>
       <c r="I104" s="25" t="n"/>
       <c r="J104" s="25" t="n"/>
-      <c r="K104" s="25" t="n"/>
+      <c r="K104" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L104" s="26" t="n"/>
       <c r="M104" s="27" t="n"/>
       <c r="N104" s="27" t="n"/>
@@ -6472,7 +6533,11 @@
       </c>
       <c r="I105" s="25" t="n"/>
       <c r="J105" s="25" t="n"/>
-      <c r="K105" s="25" t="n"/>
+      <c r="K105" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L105" s="26" t="n"/>
       <c r="M105" s="27" t="n"/>
       <c r="N105" s="27" t="n"/>
@@ -6568,7 +6633,11 @@
       </c>
       <c r="I107" s="25" t="n"/>
       <c r="J107" s="25" t="n"/>
-      <c r="K107" s="25" t="n"/>
+      <c r="K107" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L107" s="26" t="n"/>
       <c r="M107" s="27" t="n"/>
       <c r="N107" s="27" t="n"/>
@@ -6772,7 +6841,11 @@
       </c>
       <c r="I111" s="25" t="n"/>
       <c r="J111" s="25" t="n"/>
-      <c r="K111" s="25" t="n"/>
+      <c r="K111" s="25" t="inlineStr">
+        <is>
+          <t>https://thecybersec.gr/mitroo-politikon/</t>
+        </is>
+      </c>
       <c r="L111" s="26" t="n"/>
       <c r="M111" s="27" t="n"/>
       <c r="N111" s="27" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,8 @@
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-endpoint-deep-dive/
-https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/</t>
+https://thecybersec.gr/posts/previews/defender-endpoint-ai-agent-runtime-protection-intune/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="L79" s="26" t="n"/>
@@ -5235,7 +5236,8 @@
 https://thecybersec.gr/posts/defender-demystified-series/defender-demystified-part-2-four-workloads/
 https://thecybersec.gr/posts/microsoft-defender-up-close-series/microsoft-defender-for-office-365-deep-dive/
 https://thecybersec.gr/elegxos-domain/
-https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/</t>
+https://thecybersec.gr/posts/homograph-attack-kyrillika-grammata/
+https://thecybersec.gr/giati-pige-sta-junk/</t>
         </is>
       </c>
       <c r="L81" s="26" t="n"/>

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,8 @@
       <c r="J42" s="25" t="n"/>
       <c r="K42" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/entra-token-protection-bulk-enrollment-limitation/</t>
         </is>
       </c>
@@ -3153,7 +3154,8 @@
       <c r="J43" s="25" t="n"/>
       <c r="K43" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
         </is>
@@ -6376,7 +6378,8 @@
       <c r="J102" s="25" t="n"/>
       <c r="K102" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
+          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
 https://thecybersec.gr/posts/new-features/defender-identity-health-alert-network-traffic/

--- a/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
+++ b/static/downloads/nis2-kya-1689-2025-microsoft-365-checklist.xlsx
@@ -3096,7 +3096,8 @@
       <c r="J42" s="25" t="n"/>
       <c r="K42" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/entra-token-protection-bulk-enrollment-limitation/</t>
         </is>
@@ -3154,7 +3155,8 @@
       <c r="J43" s="25" t="n"/>
       <c r="K43" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/passkeys-by-default-telos-sms-voice-mfa/
 https://thecybersec.gr/posts/global-secure-access/global-secure-access-meros-5-conditional-access/
 https://thecybersec.gr/posts/secure-score-grc-part-0-intro/</t>
@@ -6378,7 +6380,8 @@
       <c r="J102" s="25" t="n"/>
       <c r="K102" s="25" t="inlineStr">
         <is>
-          <t>https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
+          <t>https://thecybersec.gr/ti-simainei-aadsts/
+https://thecybersec.gr/posts/aadsts-sfalmata-syndesis-entra-id/
 https://thecybersec.gr/posts/microsoft-defender-air-automated-investigation-response/
 https://thecybersec.gr/posts/new-features/defender-xdr-unified-identity-timeline/
 https://thecybersec.gr/posts/teams-security-detection-report/
